--- a/2022 data/excel_outputs/371_boothwise_data.xlsx
+++ b/2022 data/excel_outputs/371_boothwise_data.xlsx
@@ -478,7 +478,7 @@
     <t>P S CHANDPUR ROOM NO.2</t>
   </si>
   <si>
-    <t>P S CHANDPUR ?0??03</t>
+    <t>PRA0 PA0 GOPIPUR</t>
   </si>
   <si>
     <t>P S HAUJ UCHAVA</t>
